--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484608_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484608_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.0998</v>
+        <v>6.5554</v>
       </c>
       <c r="E2" t="n">
-        <v>6.7632</v>
+        <v>7.4913</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6634</v>
+        <v>-0.9359</v>
       </c>
       <c r="G2" t="n">
         <v>4.9473</v>
@@ -610,13 +610,13 @@
         <v>1.6493</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6929999999999999</v>
+        <v>-0.2374</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8077</v>
+        <v>-0.0795</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1147</v>
+        <v>-0.1578</v>
       </c>
       <c r="V2" t="n">
         <v>2.212</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. ROSELLO ORTS</t>
+          <t>D. FERNANDEZ NARRO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2339</v>
+        <v>3.8131</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1841</v>
+        <v>2.2018</v>
       </c>
       <c r="F3" t="n">
-        <v>3.0498</v>
+        <v>1.6112</v>
       </c>
       <c r="G3" t="n">
-        <v>3.2206</v>
+        <v>3.5468</v>
       </c>
       <c r="H3" t="n">
-        <v>1.4448</v>
+        <v>3.4348</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7758</v>
+        <v>0.112</v>
       </c>
       <c r="J3" t="n">
-        <v>1.267</v>
+        <v>3.0786</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5169</v>
+        <v>2.8702</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7501</v>
+        <v>0.2084</v>
       </c>
       <c r="M3" t="n">
-        <v>1.9535</v>
+        <v>0.4682</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9278999999999999</v>
+        <v>0.5646</v>
       </c>
       <c r="O3" t="n">
-        <v>1.0256</v>
+        <v>-0.0964</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3665</v>
+        <v>1.8326</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9163</v>
+        <v>-0.1833</v>
       </c>
       <c r="R3" t="n">
-        <v>1.2828</v>
+        <v>2.0158</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3532</v>
+        <v>-1.2547</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1666</v>
+        <v>-0.382</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1865</v>
+        <v>-0.8728</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-0.3115</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>-0.3115</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ NARRO</t>
+          <t>P. ROSELLO ORTS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9552</v>
+        <v>3.0194</v>
       </c>
       <c r="E4" t="n">
-        <v>1.666</v>
+        <v>0.143</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2892</v>
+        <v>2.8764</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5468</v>
+        <v>3.2206</v>
       </c>
       <c r="H4" t="n">
-        <v>3.4348</v>
+        <v>1.4448</v>
       </c>
       <c r="I4" t="n">
-        <v>0.112</v>
+        <v>1.7758</v>
       </c>
       <c r="J4" t="n">
-        <v>3.0786</v>
+        <v>1.267</v>
       </c>
       <c r="K4" t="n">
-        <v>2.8702</v>
+        <v>0.5169</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2084</v>
+        <v>0.7501</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4682</v>
+        <v>1.9535</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5646</v>
+        <v>0.9278999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0964</v>
+        <v>1.0256</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8326</v>
+        <v>0.3665</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1833</v>
+        <v>-0.9163</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0158</v>
+        <v>1.2828</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.1126</v>
+        <v>-0.5677</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9177999999999999</v>
+        <v>-0.2077</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.1948</v>
+        <v>-0.3599</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3115</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.3115</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2633</v>
+        <v>2.8085</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0524</v>
+        <v>1.1765</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2108</v>
+        <v>1.632</v>
       </c>
       <c r="G5" t="n">
         <v>1.1483</v>
@@ -844,13 +844,13 @@
         <v>2.0158</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7464</v>
+        <v>-0.2012</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4367</v>
+        <v>0.5607</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.1831</v>
+        <v>-0.7619</v>
       </c>
       <c r="V5" t="n">
         <v>0.945</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. FAJARDO PAÑOS</t>
+          <t>C. FAJARDO PANOS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3251</v>
+        <v>0.3382</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3251</v>
+        <v>0.7173</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>-0.3791</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3251</v>
+        <v>1.2088</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3251</v>
+        <v>-0.4229</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1.6317</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3251</v>
+        <v>2.0928</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3251</v>
+        <v>0.1084</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.9845</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-0.884</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-0.5312</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-0.3528</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-1.2828</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.0158</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.733</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.4121</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.6403</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>-0.2281</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. RUBIO MONFORT</t>
+          <t>C. FAJARDO PAÑOS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1833</v>
+        <v>0.3251</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.3251</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1833</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2564</v>
+        <v>0.3251</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2564</v>
+        <v>0.3251</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>0.3251</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.3251</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2564</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2564</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1833</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1833</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2564</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2564</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. FAJARDO PANOS</t>
+          <t>J. RUBIO MONFORT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1511</v>
+        <v>0.1833</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2776</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4287</v>
+        <v>0.1833</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2088</v>
+        <v>0.2564</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4229</v>
+        <v>0.2564</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6317</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.0928</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1084</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1.9845</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.884</v>
+        <v>0.2564</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5312</v>
+        <v>0.2564</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3528</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.2828</v>
+        <v>0.1833</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.0158</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.733</v>
+        <v>0.1833</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0771</v>
+        <v>-0.2564</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2006</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2777</v>
+        <v>-0.2564</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. JIMENEZ LORENTE</t>
+          <t>M. ANDRES VALVERDE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1556</v>
+        <v>-0.2221</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4025</v>
+        <v>-0.9414</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2469</v>
+        <v>0.7193000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.2303</v>
+        <v>0.4696</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.3485</v>
+        <v>0.428</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8818</v>
+        <v>0.0417</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7584</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.9668</v>
+        <v>0.0433</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2084</v>
+        <v>0.0417</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4719</v>
+        <v>0.3846</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3818</v>
+        <v>0.3846</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0902</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.733</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.2828</v>
+        <v>-0.9163</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0158</v>
+        <v>0.5498</v>
       </c>
       <c r="S9" t="n">
-        <v>1.6532</v>
+        <v>-0.3252</v>
       </c>
       <c r="T9" t="n">
-        <v>1.6282</v>
+        <v>-0.1101</v>
       </c>
       <c r="U9" t="n">
-        <v>0.025</v>
+        <v>-0.2151</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3115</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0104</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. ANDRES VALVERDE</t>
+          <t>O. ROIG VALERO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3019</v>
+        <v>-0.7544999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9964</v>
+        <v>-2.5576</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6945</v>
+        <v>1.8031</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4696</v>
+        <v>-0.6241</v>
       </c>
       <c r="H10" t="n">
-        <v>0.428</v>
+        <v>-1.2461</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0417</v>
+        <v>0.6219</v>
       </c>
       <c r="J10" t="n">
-        <v>0.08500000000000001</v>
+        <v>-2.2816</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0433</v>
+        <v>-2.3907</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0417</v>
+        <v>0.1091</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3846</v>
+        <v>1.6575</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3846</v>
+        <v>1.1446</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>0.5128</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.3665</v>
+        <v>1.6493</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5498</v>
+        <v>1.6493</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4051</v>
+        <v>-1.1357</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1652</v>
+        <v>-0.276</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2399</v>
+        <v>-0.8597</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.6439</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F. FERRER I SEGURA</t>
+          <t>J. JIMENEZ LORENTE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.2036</v>
+        <v>-1.1531</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.502</v>
+        <v>-1.1028</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2985</v>
+        <v>-0.0503</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.5159</v>
+        <v>-2.2303</v>
       </c>
       <c r="H11" t="n">
-        <v>1.4554</v>
+        <v>-1.3485</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.9713</v>
+        <v>-0.8818</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.8972</v>
+        <v>-0.7584</v>
       </c>
       <c r="K11" t="n">
-        <v>1.2663</v>
+        <v>-0.9668</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.1635</v>
+        <v>0.2084</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3813</v>
+        <v>-1.4719</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1891</v>
+        <v>-0.3818</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1922</v>
+        <v>-1.0902</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>0.733</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.1991</v>
+        <v>-1.2828</v>
       </c>
       <c r="R11" t="n">
-        <v>2.1991</v>
+        <v>2.0158</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3123</v>
+        <v>0.6556999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>1.0053</v>
+        <v>0.928</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6929999999999999</v>
+        <v>-0.2723</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.3115</v>
       </c>
       <c r="W11" t="n">
-        <v>1.5889</v>
+        <v>0.0104</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.5889</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>O. ROIG VALERO</t>
+          <t>F. FERRER I SEGURA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.3483</v>
+        <v>-1.4885</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.0523</v>
+        <v>-2.0099</v>
       </c>
       <c r="F12" t="n">
-        <v>1.7041</v>
+        <v>0.5214</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.6241</v>
+        <v>-1.5159</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.2461</v>
+        <v>1.4554</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6219</v>
+        <v>-2.9713</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.2816</v>
+        <v>-1.8972</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.3907</v>
+        <v>1.2663</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1091</v>
+        <v>-3.1635</v>
       </c>
       <c r="M12" t="n">
-        <v>1.6575</v>
+        <v>0.3813</v>
       </c>
       <c r="N12" t="n">
-        <v>1.1446</v>
+        <v>0.1891</v>
       </c>
       <c r="O12" t="n">
-        <v>0.5128</v>
+        <v>0.1922</v>
       </c>
       <c r="P12" t="n">
-        <v>1.6493</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-2.1991</v>
       </c>
       <c r="R12" t="n">
-        <v>1.6493</v>
+        <v>2.1991</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.7296</v>
+        <v>0.0273</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7707000000000001</v>
+        <v>0.4974</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9588</v>
+        <v>-0.47</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.6439</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.5889</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.6439</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.41</v>
+        <v>-2.8336</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.2581</v>
+        <v>-2.2852</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.152</v>
+        <v>-0.5483</v>
       </c>
       <c r="G13" t="n">
         <v>-0.129</v>
@@ -1468,13 +1468,13 @@
         <v>2.1991</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8368</v>
+        <v>0.4133</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4548</v>
+        <v>0.4276</v>
       </c>
       <c r="U13" t="n">
-        <v>0.382</v>
+        <v>-0.0144</v>
       </c>
       <c r="V13" t="n">
         <v>-2.2016</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.490100000000002</v>
+        <v>10.5912</v>
       </c>
       <c r="E14" t="n">
-        <v>2.057100000000002</v>
+        <v>3.158099999999997</v>
       </c>
       <c r="F14" t="n">
-        <v>7.432999999999999</v>
+        <v>7.4331</v>
       </c>
       <c r="G14" t="n">
         <v>10.6236</v>
@@ -1525,7 +1525,7 @@
         <v>3.0844</v>
       </c>
       <c r="L14" t="n">
-        <v>5.1313</v>
+        <v>5.131299999999999</v>
       </c>
       <c r="M14" t="n">
         <v>2.408</v>
@@ -1546,22 +1546,22 @@
         <v>16.4931</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.571099999999999</v>
+        <v>-2.4699</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8976000000000002</v>
+        <v>1.9987</v>
       </c>
       <c r="U14" t="n">
-        <v>-4.468500000000001</v>
+        <v>-4.468400000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.3114999999999997</v>
+        <v>-0.3115000000000001</v>
       </c>
       <c r="W14" t="n">
         <v>6.688099999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.999400000000001</v>
+        <v>-6.9994</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.7464</v>
+        <v>3.5043</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6188</v>
+        <v>3.388</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1276</v>
+        <v>0.1162</v>
       </c>
       <c r="G15" t="n">
         <v>-0.3461</v>
@@ -1624,13 +1624,13 @@
         <v>2.3823</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9484</v>
+        <v>0.7062</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5709</v>
+        <v>0.1984</v>
       </c>
       <c r="U15" t="n">
-        <v>1.5192</v>
+        <v>0.5079</v>
       </c>
       <c r="V15" t="n">
         <v>0.945</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8294</v>
+        <v>1.0844</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2281</v>
+        <v>1.1319</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3987</v>
+        <v>-0.0475</v>
       </c>
       <c r="G18" t="n">
         <v>-1.4831</v>
@@ -1858,13 +1858,13 @@
         <v>0.5498</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4775</v>
+        <v>0.7325</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7866</v>
+        <v>0.6904</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3091</v>
+        <v>0.042</v>
       </c>
       <c r="V18" t="n">
         <v>2.2016</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. IGBINS DAVID</t>
+          <t>A. PEREZ RIPOLL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0731</v>
+        <v>0.1515</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2184</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2915</v>
+        <v>0.2177</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3649</v>
+        <v>0.3259</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1895</v>
+        <v>-0.2928</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5545</v>
+        <v>0.6187</v>
       </c>
       <c r="J19" t="n">
-        <v>1.7221</v>
+        <v>0.6725</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4302</v>
+        <v>0.0217</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2919</v>
+        <v>0.6509</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3572</v>
+        <v>-0.3466</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6198</v>
+        <v>-0.3145</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7374000000000001</v>
+        <v>-0.0321</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.2828</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R19" t="n">
         <v>0.5498</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8447</v>
+        <v>0.1921</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3288</v>
+        <v>0.1776</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5159</v>
+        <v>0.0145</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. PEREZ RIPOLL</t>
+          <t>A. IGBINS DAVID</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5958</v>
+        <v>0.0303</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7392</v>
+        <v>0.2184</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1434</v>
+        <v>-0.1881</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3259</v>
+        <v>0.3649</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2928</v>
+        <v>-0.1895</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6187</v>
+        <v>0.5545</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6725</v>
+        <v>1.7221</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0217</v>
+        <v>0.4302</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6509</v>
+        <v>1.2919</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3466</v>
+        <v>-1.3572</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3145</v>
+        <v>-0.6198</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0321</v>
+        <v>-0.7374000000000001</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3665</v>
+        <v>-1.2828</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R20" t="n">
         <v>0.5498</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5553</v>
+        <v>0.9482</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4955</v>
+        <v>0.3288</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0598</v>
+        <v>0.6193</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4145</v>
+        <v>-1.4364</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8421</v>
+        <v>-1.9382</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4275</v>
+        <v>0.5018</v>
       </c>
       <c r="G21" t="n">
         <v>-0.7937</v>
@@ -2092,13 +2092,13 @@
         <v>0.9163</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0126</v>
+        <v>-0.0092</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2187</v>
+        <v>0.1226</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2061</v>
+        <v>-0.1318</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6335</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. CAMPOS DE BENGOA</t>
+          <t>P. MORTE MONTANES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7362</v>
+        <v>-2.0579</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4532</v>
+        <v>-3.3677</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.283</v>
+        <v>1.3099</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.18</v>
+        <v>-1.9042</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.0098</v>
+        <v>-1.8654</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.1702</v>
+        <v>-0.0388</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.015</v>
+        <v>-1.0077</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.7746</v>
+        <v>-1.2577</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.2404</v>
+        <v>0.25</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.165</v>
+        <v>-0.8965</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2351</v>
+        <v>-0.6077</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-0.2888</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.1833</v>
+        <v>-1.2828</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9163</v>
+        <v>-3.8484</v>
       </c>
       <c r="R22" t="n">
-        <v>0.733</v>
+        <v>2.5656</v>
       </c>
       <c r="S22" t="n">
-        <v>4.2056</v>
+        <v>-0.1378</v>
       </c>
       <c r="T22" t="n">
-        <v>3.7896</v>
+        <v>0.2214</v>
       </c>
       <c r="U22" t="n">
-        <v>0.416</v>
+        <v>-0.3592</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.5785</v>
+        <v>1.267</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.3115</v>
+        <v>1.267</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2949</v>
+        <v>-2.2118</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.1354</v>
+        <v>-1.4238</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1595</v>
+        <v>-0.7879</v>
       </c>
       <c r="G23" t="n">
         <v>0.9821</v>
@@ -2248,13 +2248,13 @@
         <v>2.0158</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4498</v>
+        <v>-0.3667</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4005</v>
+        <v>0.112</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8502999999999999</v>
+        <v>-0.4787</v>
       </c>
       <c r="V23" t="n">
         <v>-1.9109</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P. MORTE MONTANES</t>
+          <t>M. MARIA VENTURA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.6043</v>
+        <v>-3.0821</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.4639</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8596</v>
+        <v>-2.3426</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.9042</v>
+        <v>-3.9748</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.8654</v>
+        <v>-1.9073</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0388</v>
+        <v>-2.0675</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.0077</v>
+        <v>-1.4772</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.2577</v>
+        <v>-1.0128</v>
       </c>
       <c r="L24" t="n">
-        <v>0.25</v>
+        <v>-0.4645</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.8965</v>
+        <v>-2.4976</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.6077</v>
+        <v>-0.8946</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.2888</v>
+        <v>-1.603</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.2828</v>
+        <v>1.2828</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.8484</v>
+        <v>-0.1833</v>
       </c>
       <c r="R24" t="n">
-        <v>2.5656</v>
+        <v>1.4661</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6842</v>
+        <v>0.233</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1252</v>
+        <v>0.2772</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.8095</v>
+        <v>-0.0441</v>
       </c>
       <c r="V24" t="n">
-        <v>1.267</v>
+        <v>-0.6231</v>
       </c>
       <c r="W24" t="n">
-        <v>1.267</v>
+        <v>0.6439</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>D. GARCIA ROYO</t>
+          <t>J. CAMPOS DE BENGOA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.9139</v>
+        <v>-4.0002</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.0509</v>
+        <v>-2.5686</v>
       </c>
       <c r="F25" t="n">
-        <v>1.137</v>
+        <v>-1.4316</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.7905</v>
+        <v>-4.18</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.6684</v>
+        <v>-2.0098</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1221</v>
+        <v>-2.1702</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.0266</v>
+        <v>-3.015</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.1933</v>
+        <v>-1.7746</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1667</v>
+        <v>-1.2404</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2361</v>
+        <v>-1.165</v>
       </c>
       <c r="N25" t="n">
-        <v>0.5249</v>
+        <v>-0.2351</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.2888</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.8326</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.8484</v>
+        <v>-0.9163</v>
       </c>
       <c r="R25" t="n">
-        <v>2.0158</v>
+        <v>0.733</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0653</v>
+        <v>1.9416</v>
       </c>
       <c r="T25" t="n">
-        <v>0.8583</v>
+        <v>1.6742</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.7929</v>
+        <v>0.2673</v>
       </c>
       <c r="V25" t="n">
-        <v>0.6439</v>
+        <v>-1.5785</v>
       </c>
       <c r="W25" t="n">
-        <v>0.9658</v>
+        <v>-0.3115</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.3219</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>M. MARIA VENTURA</t>
+          <t>D. GARCIA ROYO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.6089</v>
+        <v>-4.0071</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.9894</v>
+        <v>-5.2432</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.6195</v>
+        <v>1.2361</v>
       </c>
       <c r="G26" t="n">
-        <v>-3.9748</v>
+        <v>-2.7905</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.9073</v>
+        <v>-2.6684</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.0675</v>
+        <v>-0.1221</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.4772</v>
+        <v>-3.0266</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.0128</v>
+        <v>-3.1933</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.4645</v>
+        <v>0.1667</v>
       </c>
       <c r="M26" t="n">
-        <v>-2.4976</v>
+        <v>0.2361</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.8946</v>
+        <v>0.5249</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.603</v>
+        <v>-0.2888</v>
       </c>
       <c r="P26" t="n">
-        <v>1.2828</v>
+        <v>-1.8326</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.1833</v>
+        <v>-3.8484</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4661</v>
+        <v>2.0158</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.2938</v>
+        <v>-0.0279</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.9728</v>
+        <v>0.6659</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.321</v>
+        <v>-0.6938</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.6231</v>
+        <v>0.6439</v>
       </c>
       <c r="W26" t="n">
-        <v>0.6439</v>
+        <v>0.9658</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.267</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-9.49</v>
+        <v>-8.8492</v>
       </c>
       <c r="E27" t="n">
-        <v>-7.433</v>
+        <v>-7.432899999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.0571</v>
+        <v>-1.416</v>
       </c>
       <c r="G27" t="n">
         <v>-10.6237</v>
@@ -2530,16 +2530,16 @@
         <v>-5.8152</v>
       </c>
       <c r="I27" t="n">
-        <v>-4.8085</v>
+        <v>-4.808499999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>-2.408</v>
+        <v>-2.408000000000001</v>
       </c>
       <c r="K27" t="n">
         <v>-2.7309</v>
       </c>
       <c r="L27" t="n">
-        <v>0.3225999999999998</v>
+        <v>0.3225999999999997</v>
       </c>
       <c r="M27" t="n">
         <v>-8.215699999999998</v>
@@ -2560,22 +2560,22 @@
         <v>13.7443</v>
       </c>
       <c r="S27" t="n">
-        <v>3.570999999999999</v>
+        <v>4.212000000000001</v>
       </c>
       <c r="T27" t="n">
         <v>4.4685</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.8975999999999997</v>
+        <v>-0.2566000000000001</v>
       </c>
       <c r="V27" t="n">
         <v>0.3115</v>
       </c>
       <c r="W27" t="n">
-        <v>6.999699999999999</v>
+        <v>6.9997</v>
       </c>
       <c r="X27" t="n">
-        <v>-6.688000000000001</v>
+        <v>-6.688</v>
       </c>
     </row>
   </sheetData>
